--- a/Config/Excel/DT_ProfessionConfig.xlsx
+++ b/Config/Excel/DT_ProfessionConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\UnrealDeepRock_Config_Preview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\letsdeeprock-profession-preview\com-final-serial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77A7AA6D-2068-4347-8C31-6C55C818FD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{658FA241-58C2-4D3D-823F-0E76D80269F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
   <si>
     <t>#TABLE=DT_ProfessionConfig</t>
   </si>
@@ -32,99 +32,179 @@
   </si>
   <si>
     <t>FName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>FText</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>FString</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>(RowName)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>#备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>DisplayName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CharacterAttributeRow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>PrimaryWeaponId</t>
-  </si>
-  <si>
-    <t>SecondarySlotType</t>
-  </si>
-  <si>
-    <t>SecondaryItemId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SecondaryWeaponId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillItemId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClassEquipmentId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>GrenadeIds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>GrenadeVariantSetId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>DefaultGrenadeId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArmorPerkIds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>职业ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>策划备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>显示名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>角色属性行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>主武器ID</t>
-  </si>
-  <si>
-    <t>第二槽类型(Weapon/Tool)</t>
-  </si>
-  <si>
-    <t>第二槽内容ID</t>
-  </si>
-  <si>
-    <t>可选手雷ID(英文逗号分隔)</t>
-  </si>
-  <si>
-    <t>手雷变体组ID</t>
-  </si>
-  <si>
-    <t>默认手雷ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副武器ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能型道具ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>职业特色装备ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可选技能型道具ID(英文逗号分隔)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能型道具变体组ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认技能型道具ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲候选词条ID(英文逗号分隔，后续配置5条)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Ranger</t>
-  </si>
-  <si>
-    <t>游侠样板职业</t>
-  </si>
-  <si>
-    <t>游侠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger loadout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Ranger_ArcaneCrossbow</t>
-  </si>
-  <si>
-    <t>Tool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger_SawedOffShotgun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger_ElementGrenade_Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Ranger_ConstructSpriteDrone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Ranger_ElementGrenade_Fire,Ranger_ElementGrenade_Frost,Ranger_ElementGrenade_Electric,Ranger_ElementGrenade_Acid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Ranger_ElementGrenade</t>
-  </si>
-  <si>
-    <t>Ranger_ElementGrenade_Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist loadout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Flamethrower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Revolver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer loadout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer_AssaultRifle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer_ChainsawLauncher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -471,10 +551,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -485,7 +565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -508,16 +588,22 @@
         <v>3</v>
       </c>
       <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
         <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>3</v>
       </c>
       <c r="J2" t="s">
         <v>3</v>
       </c>
+      <c r="K2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -548,69 +634,124 @@
       <c r="J3" t="s">
         <v>16</v>
       </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
